--- a/tutorials/data/input_bhp.xlsx
+++ b/tutorials/data/input_bhp.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1_PROJEKTI\2_SENERGYNETS_in_corso\4_Code\8_pandaprosumer_rep5\tutorials\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pmohanty\Git_repositories\pandaprosumer\tutorials\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{715FE6E8-197F-4699-A509-AD3BE550B5F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A873DDD-B7CE-4996-8191-AAF56E2080BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="41985" yWindow="2895" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>mode</t>
   </si>
@@ -33,12 +33,15 @@
   <si>
     <t>time</t>
   </si>
+  <si>
+    <t>t_amb_k</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -51,6 +54,14 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -60,7 +71,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -68,16 +79,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -380,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D290"/>
+  <dimension ref="A1:E290"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.5703125" bestFit="1" customWidth="1"/>
@@ -388,7 +418,7 @@
     <col min="4" max="4" width="14.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -401,8 +431,11 @@
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>0</v>
       </c>
@@ -415,8 +448,11 @@
       <c r="D2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>1.0416666666666666E-2</v>
       </c>
@@ -429,8 +465,11 @@
       <c r="D3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>2.0833333333333301E-2</v>
       </c>
@@ -443,8 +482,11 @@
       <c r="D4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>3.125E-2</v>
       </c>
@@ -457,8 +499,11 @@
       <c r="D5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E5" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>4.1666666666666699E-2</v>
       </c>
@@ -471,8 +516,11 @@
       <c r="D6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E6" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>5.2083333333333301E-2</v>
       </c>
@@ -485,8 +533,11 @@
       <c r="D7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E7" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>6.25E-2</v>
       </c>
@@ -499,8 +550,11 @@
       <c r="D8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E8" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>7.2916666666666699E-2</v>
       </c>
@@ -513,8 +567,11 @@
       <c r="D9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E9" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>8.3333333333333301E-2</v>
       </c>
@@ -527,8 +584,11 @@
       <c r="D10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E10" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>9.375E-2</v>
       </c>
@@ -541,8 +601,11 @@
       <c r="D11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E11" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>0.104166666666667</v>
       </c>
@@ -555,8 +618,11 @@
       <c r="D12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E12" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>0.114583333333333</v>
       </c>
@@ -569,8 +635,11 @@
       <c r="D13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E13" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>0.125</v>
       </c>
@@ -583,8 +652,11 @@
       <c r="D14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E14" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>0.13541666666666699</v>
       </c>
@@ -597,8 +669,11 @@
       <c r="D15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E15" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>0.14583333333333301</v>
       </c>
@@ -611,8 +686,11 @@
       <c r="D16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E16" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>0.15625</v>
       </c>
@@ -625,8 +703,11 @@
       <c r="D17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E17" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>0.16666666666666699</v>
       </c>
@@ -639,8 +720,11 @@
       <c r="D18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E18" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>0.17708333333333301</v>
       </c>
@@ -653,8 +737,11 @@
       <c r="D19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E19" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>0.1875</v>
       </c>
@@ -667,8 +754,11 @@
       <c r="D20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E20" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>0.19791666666666699</v>
       </c>
@@ -681,8 +771,11 @@
       <c r="D21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E21" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>0.20833333333333301</v>
       </c>
@@ -695,8 +788,11 @@
       <c r="D22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E22" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>0.21875</v>
       </c>
@@ -709,8 +805,11 @@
       <c r="D23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E23" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>0.22916666666666699</v>
       </c>
@@ -723,8 +822,11 @@
       <c r="D24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E24" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>0.23958333333333301</v>
       </c>
@@ -737,8 +839,11 @@
       <c r="D25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E25" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>0.25</v>
       </c>
@@ -751,8 +856,11 @@
       <c r="D26">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E26" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>0.26041666666666702</v>
       </c>
@@ -765,8 +873,11 @@
       <c r="D27">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E27" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>0.27083333333333298</v>
       </c>
@@ -779,8 +890,11 @@
       <c r="D28">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E28" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>0.28125</v>
       </c>
@@ -793,8 +907,11 @@
       <c r="D29">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E29" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>0.29166666666666702</v>
       </c>
@@ -807,8 +924,11 @@
       <c r="D30">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E30" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>0.30208333333333298</v>
       </c>
@@ -821,8 +941,11 @@
       <c r="D31">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E31" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>0.3125</v>
       </c>
@@ -835,8 +958,11 @@
       <c r="D32">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E32" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>0.32291666666666702</v>
       </c>
@@ -849,8 +975,11 @@
       <c r="D33">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E33" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>0.33333333333333298</v>
       </c>
@@ -863,8 +992,11 @@
       <c r="D34">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E34" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>0.34375</v>
       </c>
@@ -877,8 +1009,11 @@
       <c r="D35">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E35" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>0.35416666666666702</v>
       </c>
@@ -891,8 +1026,11 @@
       <c r="D36">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E36" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>0.36458333333333298</v>
       </c>
@@ -905,8 +1043,11 @@
       <c r="D37">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E37" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>0.375</v>
       </c>
@@ -919,8 +1060,11 @@
       <c r="D38">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E38" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>0.38541666666666702</v>
       </c>
@@ -933,8 +1077,11 @@
       <c r="D39">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E39" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>0.39583333333333298</v>
       </c>
@@ -947,8 +1094,11 @@
       <c r="D40">
         <v>1</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E40" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>0.40625</v>
       </c>
@@ -961,8 +1111,11 @@
       <c r="D41">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E41" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>0.41666666666666702</v>
       </c>
@@ -975,8 +1128,11 @@
       <c r="D42">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E42" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>0.42708333333333298</v>
       </c>
@@ -989,8 +1145,11 @@
       <c r="D43">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E43" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>0.4375</v>
       </c>
@@ -1003,8 +1162,11 @@
       <c r="D44">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E44" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>0.44791666666666702</v>
       </c>
@@ -1017,8 +1179,11 @@
       <c r="D45">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E45" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>0.45833333333333298</v>
       </c>
@@ -1031,8 +1196,11 @@
       <c r="D46">
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E46" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>0.46875</v>
       </c>
@@ -1045,8 +1213,11 @@
       <c r="D47">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E47" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>0.47916666666666702</v>
       </c>
@@ -1059,8 +1230,11 @@
       <c r="D48">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E48" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>0.48958333333333298</v>
       </c>
@@ -1073,8 +1247,11 @@
       <c r="D49">
         <v>1</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E49" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>0.5</v>
       </c>
@@ -1087,8 +1264,11 @@
       <c r="D50">
         <v>2</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E50" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>0.51041666666666696</v>
       </c>
@@ -1101,8 +1281,11 @@
       <c r="D51">
         <v>2</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E51" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>0.52083333333333304</v>
       </c>
@@ -1115,8 +1298,11 @@
       <c r="D52">
         <v>2</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E52" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>0.53125</v>
       </c>
@@ -1129,8 +1315,11 @@
       <c r="D53">
         <v>2</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E53" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>0.54166666666666696</v>
       </c>
@@ -1143,8 +1332,11 @@
       <c r="D54">
         <v>2</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E54" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>0.55208333333333304</v>
       </c>
@@ -1157,8 +1349,11 @@
       <c r="D55">
         <v>2</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E55" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>0.5625</v>
       </c>
@@ -1171,8 +1366,11 @@
       <c r="D56">
         <v>2</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E56" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>0.57291666666666696</v>
       </c>
@@ -1185,8 +1383,11 @@
       <c r="D57">
         <v>2</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E57" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>0.58333333333333304</v>
       </c>
@@ -1199,8 +1400,11 @@
       <c r="D58">
         <v>2</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E58" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>0.59375</v>
       </c>
@@ -1213,8 +1417,11 @@
       <c r="D59">
         <v>2</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E59" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>0.60416666666666696</v>
       </c>
@@ -1227,8 +1434,11 @@
       <c r="D60">
         <v>2</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E60" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>0.61458333333333304</v>
       </c>
@@ -1241,8 +1451,11 @@
       <c r="D61">
         <v>2</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E61" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>0.625</v>
       </c>
@@ -1255,8 +1468,11 @@
       <c r="D62">
         <v>2</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E62" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>0.63541666666666696</v>
       </c>
@@ -1269,8 +1485,11 @@
       <c r="D63">
         <v>2</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E63" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>0.64583333333333304</v>
       </c>
@@ -1283,8 +1502,11 @@
       <c r="D64">
         <v>2</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E64" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>0.65625</v>
       </c>
@@ -1297,8 +1519,11 @@
       <c r="D65">
         <v>2</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E65" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>0.66666666666666696</v>
       </c>
@@ -1311,8 +1536,11 @@
       <c r="D66">
         <v>2</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E66" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>0.67708333333333304</v>
       </c>
@@ -1325,8 +1553,11 @@
       <c r="D67">
         <v>2</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E67" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>0.6875</v>
       </c>
@@ -1339,8 +1570,11 @@
       <c r="D68">
         <v>2</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E68" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>0.69791666666666696</v>
       </c>
@@ -1353,8 +1587,11 @@
       <c r="D69">
         <v>2</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E69" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>0.70833333333333304</v>
       </c>
@@ -1367,8 +1604,11 @@
       <c r="D70">
         <v>2</v>
       </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E70" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>0.71875</v>
       </c>
@@ -1381,8 +1621,11 @@
       <c r="D71">
         <v>2</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E71" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>0.72916666666666696</v>
       </c>
@@ -1395,8 +1638,11 @@
       <c r="D72">
         <v>2</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E72" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>0.73958333333333304</v>
       </c>
@@ -1409,8 +1655,11 @@
       <c r="D73">
         <v>2</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E73" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>0.75</v>
       </c>
@@ -1423,8 +1672,11 @@
       <c r="D74">
         <v>1</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E74" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>0.76041666666666696</v>
       </c>
@@ -1437,8 +1689,11 @@
       <c r="D75">
         <v>1</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E75" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>0.77083333333333304</v>
       </c>
@@ -1451,8 +1706,11 @@
       <c r="D76">
         <v>1</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E76" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>0.78125</v>
       </c>
@@ -1465,8 +1723,11 @@
       <c r="D77">
         <v>1</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E77" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>0.79166666666666696</v>
       </c>
@@ -1479,8 +1740,11 @@
       <c r="D78">
         <v>1</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E78" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>0.80208333333333304</v>
       </c>
@@ -1493,8 +1757,11 @@
       <c r="D79">
         <v>1</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E79" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>0.8125</v>
       </c>
@@ -1507,8 +1774,11 @@
       <c r="D80">
         <v>1</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E80" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>0.82291666666666696</v>
       </c>
@@ -1521,8 +1791,11 @@
       <c r="D81">
         <v>1</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E81" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>0.83333333333333304</v>
       </c>
@@ -1535,8 +1808,11 @@
       <c r="D82">
         <v>1</v>
       </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E82" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>0.84375</v>
       </c>
@@ -1549,8 +1825,11 @@
       <c r="D83">
         <v>1</v>
       </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E83" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>0.85416666666666696</v>
       </c>
@@ -1563,8 +1842,11 @@
       <c r="D84">
         <v>1</v>
       </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E84" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>0.86458333333333304</v>
       </c>
@@ -1577,8 +1859,11 @@
       <c r="D85">
         <v>1</v>
       </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E85" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>0.875</v>
       </c>
@@ -1591,8 +1876,11 @@
       <c r="D86">
         <v>1</v>
       </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E86" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>0.88541666666666696</v>
       </c>
@@ -1605,8 +1893,11 @@
       <c r="D87">
         <v>1</v>
       </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E87" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>0.89583333333333304</v>
       </c>
@@ -1619,8 +1910,11 @@
       <c r="D88">
         <v>1</v>
       </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E88" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>0.90625</v>
       </c>
@@ -1633,8 +1927,11 @@
       <c r="D89">
         <v>1</v>
       </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E89" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>0.91666666666666696</v>
       </c>
@@ -1647,8 +1944,11 @@
       <c r="D90">
         <v>1</v>
       </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E90" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>0.92708333333333304</v>
       </c>
@@ -1661,8 +1961,11 @@
       <c r="D91">
         <v>1</v>
       </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E91" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>0.9375</v>
       </c>
@@ -1675,8 +1978,11 @@
       <c r="D92">
         <v>1</v>
       </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E92" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
         <v>0.94791666666666696</v>
       </c>
@@ -1689,8 +1995,11 @@
       <c r="D93">
         <v>1</v>
       </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E93" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>0.95833333333333304</v>
       </c>
@@ -1703,8 +2012,11 @@
       <c r="D94">
         <v>1</v>
       </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E94" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <v>0.96875</v>
       </c>
@@ -1717,8 +2029,11 @@
       <c r="D95">
         <v>1</v>
       </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E95" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>0.97916666666666696</v>
       </c>
@@ -1731,8 +2046,11 @@
       <c r="D96">
         <v>1</v>
       </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E96" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>0.98958333333333304</v>
       </c>
@@ -1745,50 +2063,53 @@
       <c r="D97">
         <v>1</v>
       </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E97" s="3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="2"/>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="2"/>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="2"/>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="2"/>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="2"/>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="2"/>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="2"/>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="2"/>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="2"/>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="2"/>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="2"/>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="2"/>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="2"/>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="2"/>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="2"/>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.25">
